--- a/artfynd/A 6097-2024 artfynd.xlsx
+++ b/artfynd/A 6097-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 6097-2024 artfynd.xlsx
+++ b/artfynd/A 6097-2024 artfynd.xlsx
@@ -2832,7 +2832,7 @@
         <v>127170101</v>
       </c>
       <c r="B19" t="n">
-        <v>97243</v>
+        <v>97318</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>127170325</v>
       </c>
       <c r="B20" t="n">
-        <v>101622</v>
+        <v>101697</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
